--- a/diseases/d106/1990-1994.xlsx
+++ b/diseases/d106/1990-1994.xlsx
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25808,7 +25808,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">

--- a/diseases/d106/1990-1994.xlsx
+++ b/diseases/d106/1990-1994.xlsx
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25808,7 +25808,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
